--- a/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt1_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9592_escuela-basica-sendero-del-saber_nt1_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DAE9118E-F031-494F-9453-474A85082F06}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{FACFBD90-E167-495E-B69B-4A9A579F6F75}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{705D1E25-A4C6-4ECB-AAB1-8701D19BA127}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BA2D3749-230B-4AC7-805D-C2E92B750C8A}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4C87701-01DD-4BC1-AC74-28E570E44074}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3045DA34-09EB-4736-8DE9-5A10620D6CB6}"/>
 </file>